--- a/output/graficos_nacionales/plot_nacional_serie_p_aps_s_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_p_aps_s_2019.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 09:17</t>
+    <t xml:space="preserve">2026-10-05 19:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
